--- a/data/processed_data/AI_Assistant_map_TaxoConsensus_Pro_app.xlsx
+++ b/data/processed_data/AI_Assistant_map_TaxoConsensus_Pro_app.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\R proy tidy data PINV01-528\data\processed_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4096E5BA-2881-4D13-88CC-C0F833C853CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79A93DB-48B9-43A8-B799-81CF49BA10B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$114</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="318">
   <si>
     <t>SPECIES_CLEAN</t>
   </si>
@@ -499,30 +502,12 @@
     <t>Anopheles gilesi was originally described by Peryassú in 1908. It is currently recognized as a valid species belonging to the subgenus Anopheles, specifically within the Arribalzagia Series. This series is characterized by specific wing spot patterns and male genitalic features. Taxonomic stability has been maintained through various revisions of the Neotropical Anopheles fauna, confirming its distinct morphological identity from closely related species such as Anopheles intermedius and Anopheles punctimacula (Peryassú, 1908; Wilkerson &amp; Sallum, 1999).</t>
   </si>
   <si>
-    <t>Chagasia rozeboomi Causey, 1944</t>
-  </si>
-  <si>
-    <t>Chagasia rozeboomi is recognized as a valid species within the subfamily Anophelinae. It was originally described by Causey (1944) based on specimens collected in the state of Ceará, Brazil. The species is morphologically distinguished from other members of the genus, such as Chagasia fajardi, by specific characteristics in the male genitalia, larval chaetotaxy, and the distribution of scales on the wings and legs. Taxonomic reviews of the genus Chagasia continue to treat it as a distinct and valid evolutionary unit (Faran, 1979).</t>
-  </si>
-  <si>
-    <t>Nyssorhynchus rozeboomi (Causey, Deane &amp; Deane, 1944).</t>
-  </si>
-  <si>
-    <t>Originally described as Anopheles (Nyssorhynchus) rozeboomi by Causey, Deane, and Deane (1944) from specimens collected in Ceará, Brazil. The species was placed within the Argyritarsis Section of the subgenus Nyssorhynchus. Following the phylogenetic analysis and subsequent taxonomic restructuring of the tribe Anophelini, the subgenus Nyssorhynchus was elevated to genus rank (Foster et al., 2017), a classification widely adopted in Neotropical entomological studies to reflect the monophyly of the group. Consequently, the valid combination is Nyssorhynchus rozeboomi.</t>
-  </si>
-  <si>
     <t>Anopheles (Myzorhynchella) lutzii Cruz, 1901</t>
   </si>
   <si>
     <t>The species was originally described as Anopheles lutzii by Oswaldo Cruz in 1901. It is currently recognized as the type species of the subgenus Myzorhynchella Theobald. There has been historical nomenclatural confusion with Anopheles lutzi Theobald, 1901; however, Theobald's name is considered a junior secondary homonym and a synonym of Anopheles (Kerteszia) cruzii Dyar &amp; Knab, 1908. In contrast, Anopheles lutzii Cruz, 1901 remains a valid and distinct taxon within the Myzorhynchella Series (Wilkerson &amp; Sallum, 1999).</t>
   </si>
   <si>
-    <t>Chagasia roozeboomi Causey, Deane &amp; Deane, 1944</t>
-  </si>
-  <si>
-    <t>The name provided in the query "Anopheles chagasia roozebomii" appears to be a taxonomic conflation. Chagasia is a distinct genus within the subfamily Anophelinae, separate from the genus Anopheles. The species was formally described as Chagasia roozeboomi by Causey, Deane, and Deane in 1944. In entomological nomenclature, Chagasia represents the most basal lineage of the Anophelinae. Therefore, the combination of Anopheles and Chagasia in a single binomen is taxonomically incorrect (Causey et al., 1944; Harbach, 2013).</t>
-  </si>
-  <si>
     <t>The genus Anopheles was established by Johann Wilhelm Meigen in 1818. It is currently the most significant genus within the subfamily Anophelinae (Family: Culicidae). The classification is based on morphological characteristics such as the length of the maxillary palps in both sexes (roughly equal to the proboscis) and the absence of a trilobed scutellum. This taxonomic status is consistently validated in the Mosquito Taxonomic Inventory (Harbach, 2024), maintaining its position as a monophyletic group comprising seven subgenera: Anopheles, Bironella, Christya, Kerteszia, Lophopodomyia, Nyssorhynchus, and Stethomyia.</t>
   </si>
   <si>
@@ -610,12 +595,6 @@
     <t>The genus Brumptomyia was established by França and Parrot (1921) to accommodate species previously classified under Phlebotomus that exhibited distinct morphological characteristics in the male genitalia, specifically the presence of a basal tuft of setae on the gonocoxite and a simplified paramere structure. The type species is Phlebotomus brumpti Larrousse, 1920. In modern Neotropical sand fly taxonomy, Brumptomyia is recognized as a valid genus within the tribe Phlebotomini, supported by comprehensive phylogenetic and morphological revisions (Galati, 2003; 2018; Young &amp; Duncan, 1994).</t>
   </si>
   <si>
-    <t>Evandromyia (Aldamyia) lenti (Mangabeira, 1938)</t>
-  </si>
-  <si>
-    <t>The species was originally described as Flebotomus lenti by Mangabeira (1938). Following the reclassification of the Psychodidae family, it was long referred to as Lutzomyia lenti under the classification system proposed by Young and Duncan (1994). However, according to the phylogenetic classification of Galati (2003), the species is currently assigned to the genus Evandromyia Mangabeira, 1941, within the subgenus Aldamyia Galati, 1995. This classification is widely accepted in Neotropical dipterology due to the morphological characters of the spermathecae in females and the parameres in males (Galati, 2018).</t>
-  </si>
-  <si>
     <t>The species was originally described as Phlebotomus shannoni by Dyar (1929). It was later transferred to the genus Lutzomyia and eventually placed within the genus Psathyromyia based on the taxonomic revisions proposed by Barretto (1962). The current classification follows the phylogenetic and morphological criteria established by Galati (2003, 2018), which treats Psathyromyia as a distinct genus within the subtribe Psychodopygina. The species is the type species of the genus Psathyromyia.</t>
   </si>
   <si>
@@ -658,24 +637,12 @@
     <t>The species was originally described by Pinto (1926) as Phlebotomus fischeri. While it was traditionally classified under the genus Lutzomyia for several decades, the current taxonomic stability follows the phylogenetic classification proposed by Galati (2003). Galati elevated the subgenus Pintomyia (Costa Lima, 1932) to the rank of genus, placing this species within the nominate subgenus. This classification is widely accepted in Neotropical dipterology and used by the Pan American Health Organization (PAHO).</t>
   </si>
   <si>
-    <t>Trichophoromyia quinquefer (Dyar, 1929)</t>
-  </si>
-  <si>
-    <t>The species was originally described as Phlebotomus quinquefer by Dyar (1929). It was later included in the genus Lutzomyia, subgenus Trichophoromyia, as Lutzomyia quinquefer (Young &amp; Duncan, 1994). Following the phylogenetic classification proposed by Galati (2003), the subgenus Trichophoromyia was elevated to the rank of genus. Therefore, the currently accepted name in Neotropical dipterology is Trichophoromyia quinquefer (Dyar, 1929).</t>
-  </si>
-  <si>
     <t>Lutzomyia monticola (Costa Lima, 1932)</t>
   </si>
   <si>
     <t>The species was originally described by Costa Lima in 1932 as Phlebotomus monticolus. Following the taxonomic reorganization of the subfamily Phlebotominae, it was transferred to the genus Lutzomyia França, 1924. According to the classification systems of Young and Duncan (1994) and Galati (2003, 2018), the species is valid and serves as the type species for the monticola series within the subgenus Lutzomyia. The species is characterized by its distinct paramere structure and spermathecae morphology in the female.</t>
   </si>
   <si>
-    <t>Evandromyia lenti (Mangabeira, 1938)</t>
-  </si>
-  <si>
-    <t>The species was originally described by Mangabeira in 1938 under the genus Flebotomus. Following the taxonomic restructuring of the subfamily Phlebotominae, it was later classified within the genus Lutzomyia. However, according to the phylogenetic classification proposed by Galati (2003), which is widely accepted in the Neotropical region, the species is currently placed in the genus Evandromyia Mangabeira, 1941, subgenus Evandromyia. The parentheses in the author citation indicate the original description occurred in a different genus (Mangabeira, 1938).</t>
-  </si>
-  <si>
     <t>Originally described as Phlebotomus fischeri by Pinto (1926), the species was later reassigned to the genus Lutzomyia. However, following the phylogenetic reclassification of the subfamily Phlebotominae by Galati (2003), the species is currently recognized under the genus Pintomyia Costa Lima, 1932, and the subgenus Pintomyia. This taxonomic status is maintained in recent systematic revisions of Neotropical sand flies (Galati, 2018).</t>
   </si>
   <si>
@@ -727,12 +694,6 @@
     <t>Originally described as Phlebotomus migonei by França (1920), the species was later included in the genus Lutzomyia. According to the phylogenetic classification proposed by Galati (1995, 2003), it was reclassified into the genus Migonemyia. The use of the trinomial Migonemyia migonei migonei is considered obsolete in current dipterology; the species is recognized as monotypic throughout its wide distribution in South America (from Colombia to Argentina). Therefore, the repetition of the specific epithet as a subspecies is taxonomically redundant and not supported by current morphological or molecular evidence.</t>
   </si>
   <si>
-    <t>Evandromyia (Evandromyia) lenti (Mangabeira, 1938)</t>
-  </si>
-  <si>
-    <t>Originally described as Flebotomus lenti by Mangabeira in 1938, the species was later classified within the genus Lutzomyia. Following the taxonomic restructuring of the subfamily Phlebotominae by Galati (2003), it was placed in the genus Evandromyia Mangabeira, 1941, under the subgenus Evandromyia. The use of the trinomial Evandromyia lenti lenti is generally considered redundant in modern Neotropical sand fly taxonomy unless specifically contrasting it with Evandromyia lenti corumbaensis; however, most contemporary checklists (Galati, 2018, 2021) treat the species simply as Evandromyia lenti.</t>
-  </si>
-  <si>
     <t>Lutzomyia (Lutzomyia) longipalpis (Lutz &amp; Neiva, 1912)</t>
   </si>
   <si>
@@ -859,12 +820,6 @@
     <t>The taxon was originally described as Janicomyia albigenu by Peryassú in 1908. While historical literature sometimes treated it as a variety or synonym within the "janthinosoma" group or associated it with Psorophora albipes, modern taxonomic classifications recognize it as a valid species. The species is placed within the subgenus Janicomyia. Its status as a distinct species has been upheld in major taxonomic revisions and catalogs, including those by Lane (1953) and Knight &amp; Stone (1977), based on distinct morphological features of the adult female and male genitalia.</t>
   </si>
   <si>
-    <t>Haemagogus (Haemagogus) leucocelaenus (Dyar &amp; Shannon, 1924)</t>
-  </si>
-  <si>
-    <t>The taxon originally described as Haemagogus celeste by Mount (1958) is currently considered a junior synonym of Haemagogus leucocelaenus (Dyar &amp; Shannon, 1924). Extensive taxonomic revisions of the genus Haemagogus, most notably the work by Arnell (1973), concluded that the morphological variations observed in the populations described as H. celeste in Panama fall within the specific range of H. leucocelaenus. Consequently, H. celeste was formally suppressed and synonymized under the senior name Haemagogus leucocelaenus.</t>
-  </si>
-  <si>
     <t>Sabethes (Sabethoides) intermedius Lutz, 1904</t>
   </si>
   <si>
@@ -931,12 +886,6 @@
     <t>The taxon was originally described as Verrallina leucocelaena by Dyar &amp; Shannon (1924). It was later transferred to the genus Haemagogus. The name "conopostegus" mentioned in the query refers to the subgenus Conopostegus, established by Dyar (1928), to which this species belongs. According to the systematic revision by Arnell (1973) and the world catalog by Knight &amp; Stone (1977), Haemagogus leucocelaenus is the valid specific name, while Conopostegus is its subgeneric classification. There is no valid subspecies or specific name "conopostegus leucocelaenus" as a trinomial; rather, it represents the subgenus and species combination.</t>
   </si>
   <si>
-    <t>Georgecraigius (Horsfallius) fluviatilis (Lutz, 1904)</t>
-  </si>
-  <si>
-    <t>The species was originally described as Culex fluviatilis by Lutz (1904) and subsequently placed within the genus Aedes, subgenus Ochlerotatus. Following the extensive phylogenetic revision of the tribe Aedini by Reinert, Kaiser, and Bernard (2006), the subgenus Ochlerotatus was elevated to genus rank, and several species were reassigned to new genera based on morphological and molecular evidence. Reinert et al. (2006) established the genus Georgecraigius and the subgenus Horsfallius, designating fluviatilis as the type species for the latter. While some traditional classifications maintain the broad use of Aedes, the classification of Reinert et al. (2006) is the currently accepted taxonomic status in specialized mosquito systematics databases and phylogenetic frameworks used by project PINV01-528.</t>
-  </si>
-  <si>
     <t>Sabethes (Sabethoides) belisarioi Neiva &amp; Pinto, 1923</t>
   </si>
   <si>
@@ -992,6 +941,42 @@
   </si>
   <si>
     <t>SPECIES_AI_Correct</t>
+  </si>
+  <si>
+    <t>Anopheles (Nyssorhynchus) rozeboomi Causey, Bramwell &amp; Deane, 1944</t>
+  </si>
+  <si>
+    <t>This taxon is frequently confused with Chagasia rozeboomi Gabaldón et al., 1940. Causey et al. described only an Anopheles in 1944. Any attribution by Causey to the genus Chagasia is a bibliographic error. The Anopheles status is maintained for specimens from project PINV01-528 collected in malaria transmission areas.</t>
+  </si>
+  <si>
+    <t>Chagasia rozeboomi Causey, Deane &amp; Deane, 1945</t>
+  </si>
+  <si>
+    <t>This species was formally described and established by Causey, Deane, and Deane (1945) based on morphological characteristics observed in specimens from Ceará, Brazil. It is currently recognized as a valid species within the genus Chagasia (Subfamily Anophelinae). Unlike other members of the subfamily, the genus Chagasia is considered more primitive, and C. rozeboomi is distinguished from its congeners (such as C. bathana or C. fajardi) by specific patterns in the wing scales and male genitalia.</t>
+  </si>
+  <si>
+    <t>Haemagogus (Haemagogus) celeste Dyar, 1921</t>
+  </si>
+  <si>
+    <t>The tLa especie fue descrita originalmente por Harrison G. Dyar en 1921 a partir de especímenes recolectados en Trinidad. Pertenece al subgénero Haemagogus y se distingue de otras especies del género por la morfología de la genitalia del macho y el patrón de escamas metálicas en el tórax y abdomen. La validez taxonómica de Haemagogus celeste ha sido ratificada en revisiones sistemáticas profundas de la tribu Aedini y del género en la región Neotropical (Arnell, 1973), manteniéndose como un nombre aceptado en las bases de datos zoológicas actuales.</t>
+  </si>
+  <si>
+    <t>Aedes (Ochlerotatus) fluviatilis (Lutz, 1904)</t>
+  </si>
+  <si>
+    <t>Originalmente descrita como Culex fluviatilis por Lutz en 1904, la especie fue posteriormente transferida al género Aedes. Durante la reasignación taxonómica propuesta por Reinert et al. (2004), el subgénero Ochlerotatus fue elevado a nivel de género, clasificando a esta especie como Ochlerotatus fluviatilis. Sin embargo, siguiendo los criterios de Wilkerson et al. (2015), se ha restablecido la clasificación que considera a Ochlerotatus como un subgénero dentro de Aedes para mantener la estabilidad nomenclatural. Por lo tanto, el nombre aceptado actualmente bajo el consenso taxonómico mayoritario es Aedes fluviatilis.</t>
+  </si>
+  <si>
+    <t>Evandromyia (Evandromyia) lenti (Mangabeira, 1938)</t>
+  </si>
+  <si>
+    <t>La especie fue descrita originalmente por Mangabeira en 1938 bajo el nombre de Flebotomus lenti. Posteriormente, fue transferida al género Lutzomyia y clasificada dentro del subgénero Evandromyia por Young y Duncan (1994). Sin embargo, siguiendo la clasificación filogenética propuesta por Galati (2003), el subgénero fue elevado a nivel de género, estableciéndose el nombre actual como Evandromyia lenti. Esta clasificación es la más aceptada en los estudios taxonómicos contemporáneos de la fauna de flebotominos neotropicales.</t>
+  </si>
+  <si>
+    <t>La especie fue descrita originalmente por Mangabeira en 1938 bajo el nombre de Phlebotomus lenti. Posteriormente, tras las revisiones taxonómicas de la subfamilia Phlebotominae, fue transferida al género Evandromyia Mangabeira, 1941. Según la clasificación filogenética propuesta por Galati (2003, 2021), se ubica dentro del subgénero Evandromyia, basándose en la morfología característica del cibario en las hembras (presencia de dientes horizontales y verticales bien desarrollados) y la estructura de los parámetros y el edeago en los machos.</t>
+  </si>
+  <si>
+    <t>La especie fue descrita originalmente por Mangabeira en 1938 bajo el nombre Flebotomus lenti. Posteriormente, tras las revisiones taxonómicas de la familia Psychodidae, subfamilia Phlebotominae, fue transferida al género Evandromyia establecido por el mismo autor en 1941. De acuerdo con la clasificación filogenética propuesta por Galati (2003, 2018) y ampliamente aceptada en la región neotropical, se ubica en el subgénero Evandromyia, serie lenti. El uso del nombre subespecífico (trinominal) es actualmente redundante en la literatura técnica moderna, prefiriéndose el binomio Evandromyia lenti, a menos que se realicen estudios comparativos con poblaciones geográficamente aisladas que justifiquen una subdivisión subespecífica.</t>
   </si>
 </sst>
 </file>
@@ -1364,9 +1349,9 @@
   <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="1" max="1" width="59.08984375" customWidth="1"/>
+    <col min="2" max="2" width="62.1796875" customWidth="1"/>
+    <col min="3" max="3" width="100.26953125" customWidth="1"/>
     <col min="4" max="4" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1375,13 +1360,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1697,10 +1682,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>159</v>
+        <v>308</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>309</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>130</v>
@@ -1711,10 +1696,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>161</v>
+        <v>306</v>
       </c>
       <c r="C25" t="s">
-        <v>162</v>
+        <v>307</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>130</v>
@@ -1725,10 +1710,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>130</v>
@@ -1739,10 +1724,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>165</v>
+        <v>306</v>
       </c>
       <c r="C27" t="s">
-        <v>166</v>
+        <v>307</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>130</v>
@@ -1756,7 +1741,7 @@
         <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>130</v>
@@ -1767,10 +1752,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C29" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>130</v>
@@ -1784,7 +1769,7 @@
         <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>130</v>
@@ -1795,10 +1780,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C31" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>130</v>
@@ -1809,10 +1794,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>130</v>
@@ -1823,10 +1808,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C33" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>130</v>
@@ -1837,10 +1822,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C34" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>130</v>
@@ -1851,10 +1836,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>130</v>
@@ -1865,10 +1850,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>130</v>
@@ -1879,10 +1864,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C37" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>130</v>
@@ -1893,10 +1878,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C38" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>130</v>
@@ -1907,10 +1892,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C39" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>130</v>
@@ -1921,10 +1906,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C40" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>130</v>
@@ -1935,10 +1920,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>130</v>
@@ -1949,10 +1934,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>130</v>
@@ -1963,10 +1948,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C43" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>130</v>
@@ -1977,10 +1962,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C44" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>130</v>
@@ -1991,10 +1976,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>314</v>
       </c>
       <c r="C45" t="s">
-        <v>197</v>
+        <v>315</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>130</v>
@@ -2005,10 +1990,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C46" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>130</v>
@@ -2019,10 +2004,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C47" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>130</v>
@@ -2033,10 +2018,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>130</v>
@@ -2047,10 +2032,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C49" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>130</v>
@@ -2061,10 +2046,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>130</v>
@@ -2075,10 +2060,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C51" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>130</v>
@@ -2089,10 +2074,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C52" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>130</v>
@@ -2103,10 +2088,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C53" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>130</v>
@@ -2117,10 +2102,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C54" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>130</v>
@@ -2131,10 +2116,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C55" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>130</v>
@@ -2145,10 +2130,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>216</v>
+        <v>314</v>
       </c>
       <c r="C56" t="s">
-        <v>217</v>
+        <v>316</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>130</v>
@@ -2159,10 +2144,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C57" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>130</v>
@@ -2173,10 +2158,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C58" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>130</v>
@@ -2187,10 +2172,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C59" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>130</v>
@@ -2201,10 +2186,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="C60" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>130</v>
@@ -2215,10 +2200,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C61" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>130</v>
@@ -2229,10 +2214,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C62" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>130</v>
@@ -2243,10 +2228,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="C63" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>130</v>
@@ -2257,10 +2242,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C64" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>130</v>
@@ -2271,10 +2256,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C65" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>130</v>
@@ -2285,10 +2270,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="C66" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>130</v>
@@ -2299,10 +2284,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>235</v>
+        <v>314</v>
       </c>
       <c r="C67" t="s">
-        <v>236</v>
+        <v>317</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>130</v>
@@ -2313,10 +2298,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="C68" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>130</v>
@@ -2327,10 +2312,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C69" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>130</v>
@@ -2341,10 +2326,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C70" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>130</v>
@@ -2355,10 +2340,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>215</v>
+      </c>
+      <c r="C71" t="s">
         <v>227</v>
-      </c>
-      <c r="C71" t="s">
-        <v>241</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>130</v>
@@ -2369,10 +2354,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>130</v>
@@ -2383,10 +2368,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C73" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>130</v>
@@ -2397,10 +2382,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C74" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>130</v>
@@ -2411,10 +2396,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C75" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>130</v>
@@ -2425,10 +2410,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C76" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>130</v>
@@ -2439,10 +2424,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C77" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>130</v>
@@ -2453,10 +2438,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="C78" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>130</v>
@@ -2467,10 +2452,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C79" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>130</v>
@@ -2481,10 +2466,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C80" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>130</v>
@@ -2495,10 +2480,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C81" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>130</v>
@@ -2509,10 +2494,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>130</v>
@@ -2523,10 +2508,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>130</v>
@@ -2537,10 +2522,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>130</v>
@@ -2551,10 +2536,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="C85" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>130</v>
@@ -2565,10 +2550,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C86" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>130</v>
@@ -2579,10 +2564,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C87" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>130</v>
@@ -2593,10 +2578,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="C88" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>130</v>
@@ -2607,10 +2592,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="C89" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>130</v>
@@ -2621,10 +2606,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C90" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>130</v>
@@ -2635,10 +2620,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="C91" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>130</v>
@@ -2649,10 +2634,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="C92" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>130</v>
@@ -2663,10 +2648,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="C93" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>130</v>
@@ -2677,10 +2662,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="C94" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>130</v>
@@ -2691,10 +2676,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="C95" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>130</v>
@@ -2705,10 +2690,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="C96" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>130</v>
@@ -2719,10 +2704,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="C97" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>130</v>
@@ -2733,10 +2718,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="C98" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>130</v>
@@ -2747,10 +2732,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="C99" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>130</v>
@@ -2761,10 +2746,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="C100" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>130</v>
@@ -2775,10 +2760,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="C101" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>130</v>
@@ -2789,10 +2774,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="C102" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>130</v>
@@ -2803,10 +2788,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="C103" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>130</v>
@@ -2817,10 +2802,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="C104" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>130</v>
@@ -2831,10 +2816,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C105" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>130</v>
@@ -2845,10 +2830,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C106" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>130</v>
@@ -2859,10 +2844,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="C107" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>130</v>
@@ -2873,10 +2858,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="C108" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>130</v>
@@ -2887,10 +2872,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="C109" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>130</v>
@@ -2901,10 +2886,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="C110" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>130</v>
@@ -2915,10 +2900,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="C111" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>130</v>
@@ -2929,10 +2914,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="C112" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>130</v>
@@ -2943,10 +2928,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="C113" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>130</v>
@@ -2957,21 +2942,23 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="C114" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>130</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D114" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{62DCB745-3CF4-4393-B975-22F6D60D4289}"/>
     <hyperlink ref="D3:D114" r:id="rId2" display="https://gemini.google.com/share/1becd26ba066" xr:uid="{D8491E40-06A3-4E77-B760-9C153BFABA46}"/>
     <hyperlink ref="D16" r:id="rId3" xr:uid="{18F847A1-B398-4709-90EC-48FCC3CB2E83}"/>
+    <hyperlink ref="D54" r:id="rId4" xr:uid="{562B8037-8CC6-4A7F-AE05-8755B7715C9F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/processed_data/AI_Assistant_map_TaxoConsensus_Pro_app.xlsx
+++ b/data/processed_data/AI_Assistant_map_TaxoConsensus_Pro_app.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\R proy tidy data PINV01-528\data\processed_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79A93DB-48B9-43A8-B799-81CF49BA10B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3874458F-95FE-4246-A7BE-3C6E7FE1EBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$114</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="300">
   <si>
     <t>SPECIES_CLEAN</t>
   </si>
@@ -415,9 +415,6 @@
     <t>The species was originally described by Francis Metcalf Root in 1926 based on specimens collected in Brazil. It is classified within the family Culicidae, subfamily Anophelinae, genus Anopheles, and subgenus Nyssorhynchus. It belongs to the Argyritarsis Section and the Darlingi Series. Although some recent molecular phylogenies have proposed elevating Nyssorhynchus to the genus level (Foster et al., 2017), the taxonomic standard maintained by the Walter Reed Biosystematics Unit (WRBU) and major Neotropical mosquito databases continues to recognize it as a subgenus within Anopheles (Root, 1926; Harbach, 2024).</t>
   </si>
   <si>
-    <t>https://gemini.google.com/share/1becd26ba066</t>
-  </si>
-  <si>
     <t>Anopheles (Nyssorhynchus) oswaldoi (Peryassú, 1922)</t>
   </si>
   <si>
@@ -454,12 +451,6 @@
     <t>The species was formally described by Arnoldo Gabaldón in 1940. It is currently recognized as a species complex (Anopheles nuneztovari sensu lato), which includes several morphologically similar but genetically distinct lineages, such as Anopheles nuneztovari s.s., An. goeldii, and An. dunhami. Despite the ongoing taxonomic refinements using molecular tools, Anopheles nuneztovari remains a valid and widely accepted name for this group of significant Neotropical malaria vectors (Gabaldón, 1940; Conn et al., 1993).</t>
   </si>
   <si>
-    <t>Anopheles (Kerteszia) lutzii Cruz, 1901</t>
-  </si>
-  <si>
-    <t>The species was originally described by Oswaldo G. Cruz in 1901. It belongs to the subgenus Kerteszia, a group of Neotropical mosquitoes whose larvae typically develop in the water held by bromeliads. Historically, there was taxonomic confusion involving Anopheles lutzii Theobald, 1901; however, Theobald's name is considered a junior homonym and is often treated as a synonym of Anopheles (Nyssorhynchus) albitarsis or associated with Anopheles cruzii. The name Anopheles (Kerteszia) lutzii Cruz, 1901 remains the valid nomenclature for this specific taxon within the Kerteszia subgenus (Zavortink, 1973).</t>
-  </si>
-  <si>
     <t>Anopheles (Nyssorhynchus) braziliensis (Chagas, 1907)</t>
   </si>
   <si>
@@ -517,12 +508,6 @@
     <t>The species was originally described as Culex scapularis by Rondani in 1848. For much of the 20th century, it was classified within the genus Aedes. Following the taxonomic reclassification proposed by Reinert (2000), the subgenus Ochlerotatus was elevated to generic rank, leading to the combination Ochlerotatus scapularis. However, subsequent phylogenetic analyses and a push for taxonomic stability led Wilkerson et al. (2015) to propose returning Ochlerotatus to subgeneric status within Aedes. Currently, most international databases and entomological authorities, such as the Walter Reed Biosystematics Unit (WRBU), recognize the valid name as Aedes scapularis.</t>
   </si>
   <si>
-    <t>Lutzomyia longipalpis (Lutz &amp; Neiva, 1912)</t>
-  </si>
-  <si>
-    <t>The species was originally described as Phlebotomus longipalpis by Lutz and Neiva in 1912 based on specimens collected in Brazil. It was later reassigned to the genus Lutzomyia by França (1924) and remains the type species of the genus. Current taxonomic consensus acknowledges that Lutzomyia longipalpis represents a complex of sibling species rather than a single monotypic taxon, evidenced by variations in male pheromones, acoustic signals, and molecular markers (Arrivillaga &amp; Feliciangeli, 2001). However, until these members are formally described as individual species, Lutzomyia longipalpis remains the valid taxonomic name used in medical and entomological literature.</t>
-  </si>
-  <si>
     <t>Nyssomyia neivai (Pinto, 1926)</t>
   </si>
   <si>
@@ -541,12 +526,6 @@
     <t>Originally described by Larrousse (1920) under the name Phlebotomus brumpti based on specimens collected in Brazil. The species was later assigned as the type species of the genus Brumptomyia by França and Parrot (1921). The taxonomic status is widely accepted in modern Neotropical sand fly classification systems (Galati, 2003; Young &amp; Duncan, 1994), which distinguish Brumptomyia from Lutzomyia based on the morphology of the male genitalia (specifically the presence of a basal tuft of setae on the coxite) and the cibarium in females.</t>
   </si>
   <si>
-    <t>Migonemyia migonei (França, 1920)</t>
-  </si>
-  <si>
-    <t>Originally described as Phlebotomus migonei by França (1920) based on specimens collected in Paraguay. It was later reassigned to the genus Migonemyia by Galati (1995) during the phylogenetic reclassification of the subtribe Lutzomyiina. The species is the type species of the genus Migonemyia and is widely recognized under this binomen in current Neotropical dipterology (Galati, 2021).</t>
-  </si>
-  <si>
     <t>Nyssomyia whitmani (Antunes &amp; Coutinho, 1939)</t>
   </si>
   <si>
@@ -577,12 +556,6 @@
     <t>Originally described as Phlebotomus neivai by Pinto (1926), this species was long considered a junior synonym of Lutzomyia intermedia. However, Marcondes (1996) revalidated the species based on morphological differences in the female spermathecae and male terminalia, establishing the intermedia complex. Under the phylogenetic classification system proposed by Galati (2003), which is widely adopted in the Neotropics and supported by the PINV01-528 project framework, the subgenus Nyssomyia was elevated to the genus level. Therefore, the currently accepted combination is Nyssomyia neivai.</t>
   </si>
   <si>
-    <t>Evandromyia (Evandromyia) cortelezzii (Brèthes, 1923)</t>
-  </si>
-  <si>
-    <t>The species was originally described by Brèthes (1923) under the genus Phlebotomus as Phlebotomus cortelezzii. Following the phylogenetic classification proposed by Galati (2003), it was placed within the genus Evandromyia Mangabeira, 1941, subgenus Evandromyia. It is the nominate species of the cortelezzii complex, which also includes E. sallesi and E. corumbaensis. The identification of females within this complex is particularly challenging due to high morphological similarity, often requiring the use of molecular tools or the association with sympatric males for definitive diagnostic resolution.</t>
-  </si>
-  <si>
     <t>Pintomyia (Pintomyia) pessoai (Coutinho &amp; Barretto, 1940)</t>
   </si>
   <si>
@@ -691,9 +664,6 @@
     <t>The genus Brumptomyia was established by França and Parrot (1921) to classify a group of Neotropical phlebotomine sand flies that were morphologically distinct from the genus Phlebotomus. It is recognized as a valid monophyletic genus within the subfamily Phlebotominae. Morphologically, males are distinguished by having a basal tuft of setae on the gonocoxite and relatively complex parameres, while females possess spermathecae with distinct neck-like structures and long individual ducts. According to Young and Duncan (1994), Brumptomyia species are restricted to the New World, ranging from the southern United States to northern Argentina, and are taxonomically separated from Lutzomyia sensu lato by their specific ecological niches and genital morphology.</t>
   </si>
   <si>
-    <t>Originally described as Phlebotomus migonei by França (1920), the species was later included in the genus Lutzomyia. According to the phylogenetic classification proposed by Galati (1995, 2003), it was reclassified into the genus Migonemyia. The use of the trinomial Migonemyia migonei migonei is considered obsolete in current dipterology; the species is recognized as monotypic throughout its wide distribution in South America (from Colombia to Argentina). Therefore, the repetition of the specific epithet as a subspecies is taxonomically redundant and not supported by current morphological or molecular evidence.</t>
-  </si>
-  <si>
     <t>Lutzomyia (Lutzomyia) longipalpis (Lutz &amp; Neiva, 1912)</t>
   </si>
   <si>
@@ -703,21 +673,12 @@
     <t>The taxon was originally described as Phlebotomus neivai by Pinto (1926). Following the taxonomic revisions of the subtribe Psychodopygina, it was placed within the genus Lutzomyia and later transferred to the genus Nyssomyia (Galati, 2003). Although sometimes referred to with a trinomial name in older literature or specific regional contexts, modern Phlebotominae systematics treats Nyssomyia neivai as a monotypic species. It was resurrected from synonymy with Nyssomyia intermedia by Marcondes (1996), who established morphological and bio-ecological differences between the two species, a distinction further supported by molecular studies and formal redescription (Andrade Filho et al., 2003).</t>
   </si>
   <si>
-    <t>Originally described as Phlebotomus cortelezzii (Brèthes, 1923), the species was later reassigned to the genus Lutzomyia and subsequently to Evandromyia under the subgenus Evandromyia, following the taxonomic stability provided by Galati (2003). The use of the trinomial Evandromyia cortelezzii cortelezzii is considered obsolete in modern classification; current Neotropical dipterology treats it as a species within the cortelezzii complex. This complex includes E. cortelezzii, E. sallesi, and E. corumbaensis, where females are often morphologically indistinguishable, requiring the binomial nomenclature supported by Galati (2021).</t>
-  </si>
-  <si>
     <t>Originally described as Phlebotomus puntigeniculatus by Floch and Abonnenc in 1944. It was later placed within the genus Lutzomyia, subgenus Psathyromyia. According to the phylogenetic classification proposed by Galati (2003), the subgenus Psathyromyia was elevated to generic status. The use of the trinomial Psathyromyia puntigeniculata puntigeniculata is currently deprecated in modern taxonomic revisions, as the subspecies distinctions within this taxon are not widely recognized or supported by morphological and molecular evidence. Therefore, the species is treated as a single taxon: Psathyromyia (Psathyromyia) puntigeniculata (Galati, 2018; 2021).</t>
   </si>
   <si>
     <t>The taxon was originally described as Phlebotomus brumpti by Larrousse (1920). It was later moved to the genus Brumptomyia, established by França &amp; Parrot (1921), of which it is the type species. In modern Neotropical Phlebotominae taxonomy, the use of trinomial nomenclature for this species is considered redundant or obsolete. According to the classification systems proposed by Young &amp; Duncan (1994) and updated by Galati (2018), the species is recognized as Brumptomyia brumpti. The nominate subspecies Brumptomyia brumpti brumpti is treated simply as a synonym of the species, as no valid subspecies are currently recognized within this taxon.</t>
   </si>
   <si>
-    <t>Evandromyia (Aldamyia) cortelezzii (Brethes, 1923)</t>
-  </si>
-  <si>
-    <t>Originally described as Phlebotomus cortelezzii by Brethes (1923), the species was later reassigned to the genus Evandromyia, subgenus Aldamyia, following the phylogenetic and morphological classification established by Galati (2003). The use of the trinomial Evandromyia cortelezzii cortelezzii is considered outdated in modern Neotropical dipterology; the taxon is currently recognized at the species level. It belongs to the "cortelezzii complex," which also includes E. sallesi and E. corumbaensis. This complex is characterized by the morphological similarity of females, which are often indistinguishable, requiring male terminalia for definitive specific identification (Galati, 2021).</t>
-  </si>
-  <si>
     <t>The species was originally described as Phlebotomus avellari by Costa Lima (1932). It was subsequently transferred to the genus Brumptomyia by Theodor (1948). The use of the trinomial Brumptomyia avellari avellari was used in older classifications to distinguish the nominate subspecies; however, modern taxonomic revisions and phylogenetic catalogs (Galati, 2003; Galati, 2018; Shimabukuro et al., 2017) do not recognize valid subspecies for this taxon, treating the name as Brumptomyia avellari.</t>
   </si>
   <si>
@@ -814,12 +775,6 @@
     <t>The species was originally described as Culex serratus by Theobald (1901). For much of the 20th century, it was classified under the genus Aedes, subgenus Ochlerotatus. Following the taxonomic revision by Reinert (2000), Ochlerotatus was elevated to the genus level, making the combination Ochlerotatus serratus widely used in literature. However, more recent comprehensive phylogenetic analyses and taxonomic stability efforts (Wilkerson et al., 2015) have returned Ochlerotatus to subgeneric status within the genus Aedes. Consequently, the valid name is Aedes (Ochlerotatus) serratus.</t>
   </si>
   <si>
-    <t>Psorophora (Janicomyia) albigenu (Peryassú, 1908)</t>
-  </si>
-  <si>
-    <t>The taxon was originally described as Janicomyia albigenu by Peryassú in 1908. While historical literature sometimes treated it as a variety or synonym within the "janthinosoma" group or associated it with Psorophora albipes, modern taxonomic classifications recognize it as a valid species. The species is placed within the subgenus Janicomyia. Its status as a distinct species has been upheld in major taxonomic revisions and catalogs, including those by Lane (1953) and Knight &amp; Stone (1977), based on distinct morphological features of the adult female and male genitalia.</t>
-  </si>
-  <si>
     <t>Sabethes (Sabethoides) intermedius Lutz, 1904</t>
   </si>
   <si>
@@ -886,12 +841,6 @@
     <t>The taxon was originally described as Verrallina leucocelaena by Dyar &amp; Shannon (1924). It was later transferred to the genus Haemagogus. The name "conopostegus" mentioned in the query refers to the subgenus Conopostegus, established by Dyar (1928), to which this species belongs. According to the systematic revision by Arnell (1973) and the world catalog by Knight &amp; Stone (1977), Haemagogus leucocelaenus is the valid specific name, while Conopostegus is its subgeneric classification. There is no valid subspecies or specific name "conopostegus leucocelaenus" as a trinomial; rather, it represents the subgenus and species combination.</t>
   </si>
   <si>
-    <t>Sabethes (Sabethoides) belisarioi Neiva &amp; Pinto, 1923</t>
-  </si>
-  <si>
-    <t>The species was originally described by Neiva and Pinto in 1923. It is currently recognized as a valid species belonging to the subgenus Sabethoides. Taxonomic stability has been maintained through major revisions of the Sabethini tribe, including the classifications provided by Lane (1953) and subsequently confirmed in the catalogs of Knight and Stone (1977) and the Mosquito Taxonomic Inventory. The species is distinguished from others in the subgenus by specific morphological characters of the male genitalia and the patterns of metallic scales on the thorax and legs.</t>
-  </si>
-  <si>
     <t>Sabethes (Sabethes) amazonicus Gordon &amp; Evans, 1922</t>
   </si>
   <si>
@@ -937,9 +886,6 @@
     <t>The species was originally described by Fabricius in 1794 under the name Culex ciliatus. It was later designated as the type species of the genus Psorophora by Robineau-Desvoidy in 1827. The current taxonomic classification places it within the subgenus Psorophora based on the morphological characteristics of the adult (large size, shaggy scales on legs) and larval stages, as detailed in the comprehensive revisions of the Culicidae (Knight &amp; Stone, 1977; Belkin, 1962).</t>
   </si>
   <si>
-    <t>Gemini_AI.app</t>
-  </si>
-  <si>
     <t>SPECIES_AI_Correct</t>
   </si>
   <si>
@@ -967,23 +913,23 @@
     <t>Originalmente descrita como Culex fluviatilis por Lutz en 1904, la especie fue posteriormente transferida al género Aedes. Durante la reasignación taxonómica propuesta por Reinert et al. (2004), el subgénero Ochlerotatus fue elevado a nivel de género, clasificando a esta especie como Ochlerotatus fluviatilis. Sin embargo, siguiendo los criterios de Wilkerson et al. (2015), se ha restablecido la clasificación que considera a Ochlerotatus como un subgénero dentro de Aedes para mantener la estabilidad nomenclatural. Por lo tanto, el nombre aceptado actualmente bajo el consenso taxonómico mayoritario es Aedes fluviatilis.</t>
   </si>
   <si>
-    <t>Evandromyia (Evandromyia) lenti (Mangabeira, 1938)</t>
-  </si>
-  <si>
-    <t>La especie fue descrita originalmente por Mangabeira en 1938 bajo el nombre de Flebotomus lenti. Posteriormente, fue transferida al género Lutzomyia y clasificada dentro del subgénero Evandromyia por Young y Duncan (1994). Sin embargo, siguiendo la clasificación filogenética propuesta por Galati (2003), el subgénero fue elevado a nivel de género, estableciéndose el nombre actual como Evandromyia lenti. Esta clasificación es la más aceptada en los estudios taxonómicos contemporáneos de la fauna de flebotominos neotropicales.</t>
-  </si>
-  <si>
-    <t>La especie fue descrita originalmente por Mangabeira en 1938 bajo el nombre de Phlebotomus lenti. Posteriormente, tras las revisiones taxonómicas de la subfamilia Phlebotominae, fue transferida al género Evandromyia Mangabeira, 1941. Según la clasificación filogenética propuesta por Galati (2003, 2021), se ubica dentro del subgénero Evandromyia, basándose en la morfología característica del cibario en las hembras (presencia de dientes horizontales y verticales bien desarrollados) y la estructura de los parámetros y el edeago en los machos.</t>
-  </si>
-  <si>
-    <t>La especie fue descrita originalmente por Mangabeira en 1938 bajo el nombre Flebotomus lenti. Posteriormente, tras las revisiones taxonómicas de la familia Psychodidae, subfamilia Phlebotominae, fue transferida al género Evandromyia establecido por el mismo autor en 1941. De acuerdo con la clasificación filogenética propuesta por Galati (2003, 2018) y ampliamente aceptada en la región neotropical, se ubica en el subgénero Evandromyia, serie lenti. El uso del nombre subespecífico (trinominal) es actualmente redundante en la literatura técnica moderna, prefiriéndose el binomio Evandromyia lenti, a menos que se realicen estudios comparativos con poblaciones geográficamente aisladas que justifiquen una subdivisión subespecífica.</t>
+    <t>Evandromyia (Barrettomyia) cortelezzii</t>
+  </si>
+  <si>
+    <t>La especie fue descrita originalmente por Brèthes (1923) bajo el nombre de Phlebotomus cortelezzii. Tras las revisiones taxonómicas de la subfamilia Phlebotominae, fue transferida al género Evandromyia Mangabeira, 1941, y situada dentro del subgénero Barrettomyia Martins &amp; Silva, 1968. Taxonómicamente, forma parte del "complejo cortelezzii" junto con E. sallesi y E. corumbaensis, cuyas hembras son morfológicamente indistinguibles entre sí. La validez de la especie y su posición sistemática actual están sustentadas por los criterios morfológicos y filogenéticos establecidos por Galati (2003, 2021), quien es la autoridad de referencia para la clasificación de los flebotomíneos neotropicales.</t>
+  </si>
+  <si>
+    <t>Evandromyia (Aldamyia) lenti (Mangabeira, 1938)</t>
+  </si>
+  <si>
+    <t>La especie fue descrita originalmente por Mangabeira en 1938 bajo el nombre de Phlebotomus lenti. Posteriormente, tras las revisiones taxonómicas de la subtribu Psychodopygina, fue transferida al género Evandromyia, subgénero Aldamyia. Esta clasificación es la aceptada actualmente en los catálogos taxonómicos de referencia para Phlebotominae de las Américas, basándose en la morfología de la espermateca y el proceso del estilo en los machos (Galati, 2003; 2021).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -995,14 +941,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1031,19 +969,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1346,30 +1281,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D114"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="59.08984375" customWidth="1"/>
     <col min="2" max="2" width="62.1796875" customWidth="1"/>
     <col min="3" max="3" width="100.26953125" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1379,11 +1311,8 @@
       <c r="C2" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1393,11 +1322,8 @@
       <c r="C3" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1407,11 +1333,8 @@
       <c r="C4" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1421,11 +1344,8 @@
       <c r="C5" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1435,11 +1355,8 @@
       <c r="C6" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1449,11 +1366,8 @@
       <c r="C7" t="s">
         <v>126</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1463,11 +1377,8 @@
       <c r="C8" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1477,1489 +1388,1172 @@
       <c r="C9" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" t="s">
         <v>131</v>
       </c>
-      <c r="C10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" t="s">
         <v>133</v>
       </c>
-      <c r="C11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" t="s">
         <v>138</v>
       </c>
-      <c r="C13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" t="s">
         <v>141</v>
       </c>
-      <c r="C15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s">
-        <v>146</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>155</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="C24" t="s">
-        <v>309</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="C25" t="s">
-        <v>307</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
-        <v>160</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="C27" t="s">
-        <v>307</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C28" t="s">
-        <v>161</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C29" t="s">
-        <v>163</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C30" t="s">
-        <v>161</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>164</v>
+        <v>213</v>
       </c>
       <c r="C31" t="s">
-        <v>165</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C32" t="s">
-        <v>167</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C33" t="s">
-        <v>169</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>171</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="C35" t="s">
-        <v>173</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
-        <v>175</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C38" t="s">
-        <v>178</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C41" t="s">
-        <v>183</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>184</v>
+        <v>296</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C43" t="s">
-        <v>187</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="C45" t="s">
-        <v>315</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C46" t="s">
-        <v>190</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C47" t="s">
-        <v>191</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C48" t="s">
-        <v>193</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C49" t="s">
-        <v>195</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C50" t="s">
-        <v>197</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C51" t="s">
-        <v>199</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C52" t="s">
-        <v>201</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C53" t="s">
-        <v>203</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C54" t="s">
-        <v>208</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C55" t="s">
-        <v>205</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="C56" t="s">
-        <v>316</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C57" t="s">
-        <v>206</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C58" t="s">
-        <v>208</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C59" t="s">
-        <v>210</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C60" t="s">
-        <v>212</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C61" t="s">
-        <v>214</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C62" t="s">
-        <v>216</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C64" t="s">
-        <v>219</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C65" t="s">
-        <v>221</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C66" t="s">
-        <v>222</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="C67" t="s">
-        <v>317</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C68" t="s">
-        <v>224</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
-        <v>225</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>184</v>
+        <v>296</v>
       </c>
       <c r="C70" t="s">
-        <v>226</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C71" t="s">
-        <v>227</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>228</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>229</v>
+        <v>296</v>
       </c>
       <c r="C73" t="s">
-        <v>230</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C74" t="s">
-        <v>231</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C75" t="s">
-        <v>232</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C76" t="s">
-        <v>233</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="C77" t="s">
-        <v>235</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C78" t="s">
-        <v>237</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="C79" t="s">
-        <v>239</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C80" t="s">
-        <v>241</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="C81" t="s">
-        <v>243</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C82" t="s">
-        <v>245</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="C83" t="s">
-        <v>247</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="C84" t="s">
-        <v>249</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C85" t="s">
-        <v>251</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="C86" t="s">
-        <v>253</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="C87" t="s">
-        <v>255</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C88" t="s">
-        <v>257</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="C89" t="s">
-        <v>259</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C90" t="s">
-        <v>260</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C91" t="s">
-        <v>262</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C92" t="s">
-        <v>264</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="C93" t="s">
-        <v>311</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="C94" t="s">
-        <v>266</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C95" t="s">
-        <v>268</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="C96" t="s">
-        <v>270</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="C97" t="s">
-        <v>272</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="C98" t="s">
-        <v>274</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="C99" t="s">
-        <v>276</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="C100" t="s">
-        <v>278</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="C101" t="s">
-        <v>280</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="C102" t="s">
-        <v>282</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C103" t="s">
-        <v>284</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="C104" t="s">
-        <v>286</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="C105" t="s">
-        <v>313</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="C106" t="s">
-        <v>288</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="C107" t="s">
-        <v>290</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="C108" t="s">
-        <v>292</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="C109" t="s">
-        <v>294</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="C110" t="s">
-        <v>296</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="C111" t="s">
-        <v>298</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C112" t="s">
-        <v>299</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C113" t="s">
-        <v>301</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="C114" t="s">
-        <v>303</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>130</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D114" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{62DCB745-3CF4-4393-B975-22F6D60D4289}"/>
-    <hyperlink ref="D3:D114" r:id="rId2" display="https://gemini.google.com/share/1becd26ba066" xr:uid="{D8491E40-06A3-4E77-B760-9C153BFABA46}"/>
-    <hyperlink ref="D16" r:id="rId3" xr:uid="{18F847A1-B398-4709-90EC-48FCC3CB2E83}"/>
-    <hyperlink ref="D54" r:id="rId4" xr:uid="{562B8037-8CC6-4A7F-AE05-8755B7715C9F}"/>
-  </hyperlinks>
+  <autoFilter ref="A1:C114" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Anopheles (Myzorhynchella) lutzii Cruz, 1901"/>
+        <filter val="Psorophora (Janthinosoma) lutzii (Theobald, 1901)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/processed_data/AI_Assistant_map_TaxoConsensus_Pro_app.xlsx
+++ b/data/processed_data/AI_Assistant_map_TaxoConsensus_Pro_app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\R proy tidy data PINV01-528\data\processed_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3874458F-95FE-4246-A7BE-3C6E7FE1EBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E97EEB7-3D07-47DC-94BB-53092B5E31A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="298">
   <si>
     <t>SPECIES_CLEAN</t>
   </si>
@@ -406,12 +406,6 @@
     <t>Anopheles argyritarsis is the nominotypical member of the Argyritarsis Section within the subgenus Nyssorhynchus. Since its original description by Robineau-Desvoidy in 1827, the species has maintained taxonomic stability, although it was historically confused with other members of the white-tarsus group (such as An. albitarsis). It is distinguished from closely related species by the pattern of scaling on the second hindtarsomere and specific male genitalia characters. It is widely distributed across the Neotropical region, from southern Mexico to northern Argentina and the Lesser Antilles.</t>
   </si>
   <si>
-    <t>Anopheles (Lophopodomyia) parvus (Chagas, 1908)</t>
-  </si>
-  <si>
-    <t>his species was originally described by Carlos Chagas in 1908 under the name Myzorhynchella parva, based on specimens collected in Brazil. Following the taxonomic revision of the genus Anopheles and the dissolution of Myzorhynchella as a separate genus, the species was reassigned. It is currently placed within the subgenus Lophopodomyia Antunes, 1937. The validity of the species and its current taxonomic position are supported by the morphological characteristics of the adult female wing scales and male genitalia (Chagas, 1908; Lane, 1953).</t>
-  </si>
-  <si>
     <t>The species was originally described by Francis Metcalf Root in 1926 based on specimens collected in Brazil. It is classified within the family Culicidae, subfamily Anophelinae, genus Anopheles, and subgenus Nyssorhynchus. It belongs to the Argyritarsis Section and the Darlingi Series. Although some recent molecular phylogenies have proposed elevating Nyssorhynchus to the genus level (Foster et al., 2017), the taxonomic standard maintained by the Walter Reed Biosystematics Unit (WRBU) and major Neotropical mosquito databases continues to recognize it as a subgenus within Anopheles (Root, 1926; Harbach, 2024).</t>
   </si>
   <si>
@@ -889,18 +883,6 @@
     <t>SPECIES_AI_Correct</t>
   </si>
   <si>
-    <t>Anopheles (Nyssorhynchus) rozeboomi Causey, Bramwell &amp; Deane, 1944</t>
-  </si>
-  <si>
-    <t>This taxon is frequently confused with Chagasia rozeboomi Gabaldón et al., 1940. Causey et al. described only an Anopheles in 1944. Any attribution by Causey to the genus Chagasia is a bibliographic error. The Anopheles status is maintained for specimens from project PINV01-528 collected in malaria transmission areas.</t>
-  </si>
-  <si>
-    <t>Chagasia rozeboomi Causey, Deane &amp; Deane, 1945</t>
-  </si>
-  <si>
-    <t>This species was formally described and established by Causey, Deane, and Deane (1945) based on morphological characteristics observed in specimens from Ceará, Brazil. It is currently recognized as a valid species within the genus Chagasia (Subfamily Anophelinae). Unlike other members of the subfamily, the genus Chagasia is considered more primitive, and C. rozeboomi is distinguished from its congeners (such as C. bathana or C. fajardi) by specific patterns in the wing scales and male genitalia.</t>
-  </si>
-  <si>
     <t>Haemagogus (Haemagogus) celeste Dyar, 1921</t>
   </si>
   <si>
@@ -923,6 +905,18 @@
   </si>
   <si>
     <t>La especie fue descrita originalmente por Mangabeira en 1938 bajo el nombre de Phlebotomus lenti. Posteriormente, tras las revisiones taxonómicas de la subtribu Psychodopygina, fue transferida al género Evandromyia, subgénero Aldamyia. Esta clasificación es la aceptada actualmente en los catálogos taxonómicos de referencia para Phlebotominae de las Américas, basándose en la morfología de la espermateca y el proceso del estilo en los machos (Galati, 2003; 2021).</t>
+  </si>
+  <si>
+    <t>Chagasia rozeboomi Causey, Deane &amp; Deane, 1944.</t>
+  </si>
+  <si>
+    <t>Chagasia rozeboomi is a valid species within the subfamily Anophelinae. It was originally described by Causey (1944) based on specimens collected in Ceará, Brazil. The species is morphologically distinguished from other members of the genus, such as Chagasia bathana and Chagasia fajardi, by specific characteristics of the male genitalia and the ornamentation of the adult legs. Taxonomic stability has been maintained in subsequent revisions and catalogs of the Culicidae family (Knight &amp; Stone, 1977; Harbach, 2013).</t>
+  </si>
+  <si>
+    <t>The species was originally described as Myzorhynchella parva by Chagas (1907) based on specimens collected in Brazil. Following taxonomic revisions of the genus Anopheles, the group Myzorhynchella was downgraded to a section within the subgenus Nyssorhynchus. Although some recent phylogenetic proposals (Foster et al., 2017) have suggested elevating Nyssorhynchus to genus level, the traditional classification remains the standard in most international health and entomological databases for the PINV01-528 project context. The species is morphologically distinguished by its specific wing maculation and male genitalia characteristics (Lane, 1953).</t>
+  </si>
+  <si>
+    <t>Anopheles (Nyssorhynchus) parvus (Chagas, 1907)</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1275,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1295,13 +1288,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1312,7 +1305,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1323,7 +1316,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1334,7 +1327,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1345,7 +1338,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1356,7 +1349,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1367,18 +1360,18 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>297</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1386,73 +1379,73 @@
         <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" t="s">
         <v>134</v>
       </c>
-      <c r="C12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -1460,109 +1453,109 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C16" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C24" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C25" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -1570,802 +1563,802 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C26" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C27" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C28" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C29" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C31" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C32" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C34" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C35" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C36" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C37" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C41" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C42" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C43" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C44" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C45" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C46" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C47" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C48" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C50" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C51" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C52" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C53" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C54" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C55" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C56" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C57" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C58" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C59" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C60" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C61" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C62" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C63" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C64" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C65" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C66" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C67" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C68" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C69" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C70" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C71" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C72" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C73" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C74" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C75" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C76" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C77" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C78" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C79" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C80" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C81" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C82" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C83" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C84" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C85" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C86" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C87" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C88" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C89" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C90" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C91" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C92" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C93" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C94" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C95" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C96" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C97" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C98" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
@@ -2373,186 +2366,179 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C99" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C100" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C101" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C102" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C103" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C104" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C105" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C106" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C107" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C108" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C109" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C110" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C111" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C112" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C113" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C114" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C114" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Anopheles (Myzorhynchella) lutzii Cruz, 1901"/>
-        <filter val="Psorophora (Janthinosoma) lutzii (Theobald, 1901)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:C114" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/processed_data/AI_Assistant_map_TaxoConsensus_Pro_app.xlsx
+++ b/data/processed_data/AI_Assistant_map_TaxoConsensus_Pro_app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\R proy tidy data PINV01-528\data\processed_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E97EEB7-3D07-47DC-94BB-53092B5E31A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDDB4D3-9050-4BDE-929F-BFB79C5A4463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
